--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487175_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487175_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.1159</v>
+        <v>6.8623</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4859</v>
+        <v>3.0621</v>
       </c>
       <c r="F2" t="n">
-        <v>4.63</v>
+        <v>3.8002</v>
       </c>
       <c r="G2" t="n">
         <v>6.4208</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5779</v>
+        <v>1.3243</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1774</v>
+        <v>0.7536</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4005</v>
+        <v>0.5707</v>
       </c>
       <c r="V2" t="n">
         <v>1.4333</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5771</v>
+        <v>6.7774</v>
       </c>
       <c r="E3" t="n">
-        <v>4.82</v>
+        <v>4.5385</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7571</v>
+        <v>2.2389</v>
       </c>
       <c r="G3" t="n">
         <v>4.9391</v>
@@ -688,13 +688,13 @@
         <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4098</v>
+        <v>0.6101</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6954</v>
+        <v>0.4138</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2856</v>
+        <v>0.1963</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1228</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0325</v>
+        <v>1.7603</v>
       </c>
       <c r="E4" t="n">
-        <v>0.95</v>
+        <v>1.41</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.3503</v>
       </c>
       <c r="G4" t="n">
         <v>4.5062</v>
@@ -766,13 +766,13 @@
         <v>1.158</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9346</v>
+        <v>-0.2069</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3424</v>
+        <v>0.1177</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5923</v>
+        <v>-0.3246</v>
       </c>
       <c r="V4" t="n">
         <v>0.1631</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7496</v>
+        <v>1.5507</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0451</v>
+        <v>0.2741</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7947</v>
+        <v>1.2766</v>
       </c>
       <c r="G5" t="n">
         <v>6.1575</v>
@@ -844,13 +844,13 @@
         <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5248</v>
+        <v>0.2763</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1216</v>
+        <v>0.1977</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4032</v>
+        <v>0.0786</v>
       </c>
       <c r="V5" t="n">
         <v>0.3281</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2566</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7348</v>
+        <v>-0.1151</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4782</v>
+        <v>0.6388</v>
       </c>
       <c r="G6" t="n">
         <v>0.0065</v>
@@ -922,13 +922,13 @@
         <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2281</v>
+        <v>-0.4478</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7442</v>
+        <v>-0.1246</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4839</v>
+        <v>-0.3233</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>E. GÓMEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4279</v>
+        <v>-0.3225</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.7076</v>
+        <v>-0.371</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2797</v>
+        <v>0.0485</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2793</v>
+        <v>-0.5829</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6477</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6315</v>
+        <v>-0.0179</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0253</v>
+        <v>-0.0954</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8303</v>
+        <v>0.4502</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1949</v>
+        <v>-0.5455</v>
       </c>
       <c r="M7" t="n">
-        <v>0.254</v>
+        <v>-0.4875</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1826</v>
+        <v>-1.0152</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4366</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.4042</v>
+        <v>1.158</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.7203</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3161</v>
+        <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8777</v>
+        <v>-0.8976</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2406</v>
+        <v>-0.2756</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1183</v>
+        <v>-0.622</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8193</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. GÓMEZ LÓPEZ</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8499</v>
+        <v>-0.7045</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6307</v>
+        <v>-3.2882</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2192</v>
+        <v>2.5837</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5829</v>
+        <v>3.2793</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.6477</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0179</v>
+        <v>1.6315</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0954</v>
+        <v>3.0253</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4502</v>
+        <v>2.8303</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5455</v>
+        <v>0.1949</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4875</v>
+        <v>0.254</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0152</v>
+        <v>-1.1826</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5276999999999999</v>
+        <v>1.4366</v>
       </c>
       <c r="P8" t="n">
-        <v>1.158</v>
+        <v>-5.4042</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-7.7203</v>
       </c>
       <c r="R8" t="n">
-        <v>1.158</v>
+        <v>2.3161</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4251</v>
+        <v>0.6011</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5354</v>
+        <v>0.1788</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8897</v>
+        <v>0.4223</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.8193</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7451</v>
+        <v>-2.6658</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3721</v>
+        <v>-1.2125</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.373</v>
+        <v>-1.4533</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0735</v>
@@ -1156,13 +1156,13 @@
         <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0654</v>
+        <v>0.1448</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1044</v>
+        <v>0.0552</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1699</v>
+        <v>0.0896</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0648</v>
+        <v>-2.7584</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.889</v>
+        <v>-2.5291</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1758</v>
+        <v>-0.2293</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5956</v>
@@ -1234,13 +1234,13 @@
         <v>0.386</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2327</v>
+        <v>0.539</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2089</v>
+        <v>0.151</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4415</v>
+        <v>0.388</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1228</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>10.1308</v>
+        <v>11.0232</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8766000000000012</v>
+        <v>1.7688</v>
       </c>
       <c r="F11" t="n">
-        <v>9.254299999999999</v>
+        <v>9.254399999999999</v>
       </c>
       <c r="G11" t="n">
         <v>21.0574</v>
@@ -1312,13 +1312,13 @@
         <v>12.5455</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0509</v>
+        <v>1.9433</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5752999999999998</v>
+        <v>1.4676</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4755</v>
+        <v>0.4756</v>
       </c>
       <c r="V11" t="n">
         <v>2.4982</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4609</v>
+        <v>3.5454</v>
       </c>
       <c r="E12" t="n">
-        <v>4.7521</v>
+        <v>2.2486</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7088</v>
+        <v>1.2968</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0307</v>
@@ -1390,13 +1390,13 @@
         <v>4.8252</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2528</v>
+        <v>1.3372</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3923</v>
+        <v>0.8888</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1395</v>
+        <v>0.4484</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6562</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8657</v>
+        <v>0.9926</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7317</v>
+        <v>1.8319</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8661</v>
+        <v>-0.8393</v>
       </c>
       <c r="G13" t="n">
         <v>1.0263</v>
@@ -1468,13 +1468,13 @@
         <v>0.772</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9326</v>
+        <v>-0.8057</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4759</v>
+        <v>-0.3758</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4567</v>
+        <v>-0.43</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7408</v>
+        <v>0.3589</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4828</v>
+        <v>-0.039</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2236</v>
+        <v>0.3979</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.6011</v>
+        <v>-1.294</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5247</v>
+        <v>-0.3137</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0764</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1.522</v>
+        <v>0.769</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2118</v>
+        <v>2.137</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3102</v>
+        <v>-1.368</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.1231</v>
+        <v>-2.063</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7365</v>
+        <v>-2.4507</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3866</v>
+        <v>0.3877</v>
       </c>
       <c r="P14" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>4.6322</v>
+        <v>2.7021</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5699</v>
+        <v>0.5298</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8554</v>
+        <v>0.157</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7145</v>
+        <v>0.3728</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2092</v>
+        <v>0.1979</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6132</v>
+        <v>-0.3127</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4039</v>
+        <v>0.5107</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7995</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5903</v>
+        <v>0.9974</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2208</v>
+        <v>0.5212</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3695</v>
+        <v>0.4762</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7023</v>
+        <v>-0.2219</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9403</v>
+        <v>-2.2839</v>
       </c>
       <c r="F16" t="n">
-        <v>0.238</v>
+        <v>2.062</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.294</v>
+        <v>-1.6011</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3137</v>
+        <v>-1.5247</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9802999999999999</v>
+        <v>-0.0764</v>
       </c>
       <c r="J16" t="n">
-        <v>0.769</v>
+        <v>1.522</v>
       </c>
       <c r="K16" t="n">
-        <v>2.137</v>
+        <v>0.2118</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.368</v>
+        <v>1.3102</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.063</v>
+        <v>-3.1231</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.4507</v>
+        <v>-1.7365</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3877</v>
+        <v>-1.3866</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7371</v>
+        <v>0.772</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7021</v>
+        <v>4.6322</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5314</v>
+        <v>0.6071</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7442</v>
+        <v>0.0543</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2128</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0978</v>
+        <v>-0.4507</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0133</v>
+        <v>-0.3123</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.1383</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1413</v>
@@ -1780,13 +1780,13 @@
         <v>2.7021</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3425</v>
+        <v>-0.6953</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.7251</v>
+        <v>-1.0242</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3827</v>
+        <v>0.3288</v>
       </c>
       <c r="V17" t="n">
         <v>0.614</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1674</v>
+        <v>-2.1051</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1248</v>
+        <v>-1.624</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0426</v>
+        <v>-0.4811</v>
       </c>
       <c r="G18" t="n">
         <v>-4.4696</v>
@@ -1858,13 +1858,13 @@
         <v>3.4741</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5579</v>
+        <v>-0.4957</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7456</v>
+        <v>-0.2449</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8124</v>
+        <v>-0.2509</v>
       </c>
       <c r="V18" t="n">
         <v>-0.614</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4651</v>
+        <v>-3.0573</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1827</v>
+        <v>-2.2828</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2824</v>
+        <v>-0.7744</v>
       </c>
       <c r="G19" t="n">
         <v>-4.7171</v>
@@ -1936,13 +1936,13 @@
         <v>2.7021</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1289</v>
+        <v>0.5367</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7099</v>
+        <v>0.6098</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.581</v>
+        <v>-0.0731</v>
       </c>
       <c r="V19" t="n">
         <v>-0.614</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7058</v>
+        <v>-3.252</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8734</v>
+        <v>-2.4729</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8323</v>
+        <v>-0.7791</v>
       </c>
       <c r="G20" t="n">
         <v>-4.0977</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1521</v>
+        <v>-0.6983</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9518</v>
+        <v>-0.5512</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2003</v>
+        <v>-0.1471</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8507</v>
+        <v>-4.1358</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5078</v>
+        <v>-4.0071</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3429</v>
+        <v>-0.1287</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9326</v>
@@ -2092,13 +2092,13 @@
         <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0761</v>
+        <v>-0.3612</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0113</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0648</v>
+        <v>0.1494</v>
       </c>
       <c r="V21" t="n">
         <v>-0.614</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.1309</v>
+        <v>-8.128</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.2545</v>
+        <v>-9.254200000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8764999999999998</v>
+        <v>1.126499999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-21.0573</v>
@@ -2143,7 +2143,7 @@
         <v>-13.4806</v>
       </c>
       <c r="J22" t="n">
-        <v>3.237300000000001</v>
+        <v>3.2373</v>
       </c>
       <c r="K22" t="n">
         <v>10.4201</v>
@@ -2170,13 +2170,13 @@
         <v>27.0211</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0507</v>
+        <v>0.9519999999999997</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4754999999999996</v>
+        <v>-0.4756</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5752</v>
+        <v>1.4274</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4982</v>
